--- a/Calibration Data/Callibration setup.xlsx
+++ b/Calibration Data/Callibration setup.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Github\Proa-II-Electrical-Setup\Calibration Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7726C71D-8AE4-4810-A561-8B3EA959F993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70E16AE-A83C-494F-85C4-CAA04065ECEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" firstSheet="1" activeTab="1" xr2:uid="{7531ECA2-DA00-4F76-ABDC-FCF590B5A240}"/>
+    <workbookView xWindow="-23148" yWindow="4140" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7531ECA2-DA00-4F76-ABDC-FCF590B5A240}"/>
   </bookViews>
   <sheets>
-    <sheet name="HE Current Sensor" sheetId="1" r:id="rId1"/>
-    <sheet name="Voltage Divider" sheetId="2" r:id="rId2"/>
+    <sheet name="Voltage Divider (2)" sheetId="3" r:id="rId1"/>
+    <sheet name="HE Current Sensor" sheetId="1" r:id="rId2"/>
+    <sheet name="Voltage Divider" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
   <si>
     <t>Resistance</t>
   </si>
@@ -133,9 +134,6 @@
   </si>
   <si>
     <t>Adj Ave Voltage (Divided)</t>
-  </si>
-  <si>
-    <t>Outlier</t>
   </si>
   <si>
     <t>Adj Ave Reading</t>
@@ -318,31 +316,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="24">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -396,6 +429,1310 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Voltage Divider (2)'!$K$2:$K$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>306.22222222221899</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300.22222222221899</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>285.77777777778101</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>272.77777777778101</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>313.33333333333212</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>248.88888888888323</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>292.77777777777737</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>273.77777777777737</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>264.77777777777737</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>326.55555555555839</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>293.66666666666424</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>257.66666666666788</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>315.11111111110586</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>291.22222222222626</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0257-4E26-871B-7BCD515A5D30}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="770958383"/>
+        <c:axId val="770960783"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="770958383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="770960783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="770960783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="770958383"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Voltage Divider (2)'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Expected Reading</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Voltage Divider (2)'!$C$2:$C$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>25333.333333333332</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25022.222222222219</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25022.222222222219</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24977.777777777777</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24977.777777777777</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24799.999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24622.222222222219</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24577.777777777774</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24577.777777777774</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24577.777777777774</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24355.555555555555</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>24266.666666666664</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>24266.666666666664</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23911.111111111106</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>23822.222222222223</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A681-4824-9843-3DA184F73958}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Voltage Divider (2)'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual ADC Reading</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Voltage Divider (2)'!$F$2:$F$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>25033.333333333332</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24716</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24722</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24691.999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24704.999999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24486.666666666664</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24373.333333333336</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24284.999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24303.999999999996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24312.999999999996</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24028.999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>23973</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>24008.999999999996</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23596</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>23530.999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A681-4824-9843-3DA184F73958}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="810956175"/>
+        <c:axId val="810956655"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="810956175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="810956655"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="810956655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="810956175"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Voltage Divider (2)'!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Divided Voltage Difference</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Voltage Divider (2)'!$J$2:$J$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>5.6250000000000355E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7416666666666671E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.6291666666666629E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.3583333333333982E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.114583333333389E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.8749999999999858E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.6666666666665968E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.4895833333333144E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.1333333333333009E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.9645833333332945E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.1229166666667112E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.5062500000000014E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.8312500000000647E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.908333333333271E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.4604166666667453E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2848-448F-8036-D93E901AC33F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Voltage Divider (2)'!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Adjusted Voltage Difference</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Voltage Divider (2)'!$L$2:$L$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>3.5107964324865293E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.204224279208411E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0792242792083684E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.5310407727966435E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-3.9685407727967359E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0278990191797703E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.6631611888435813E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.6407375915122913E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-2.8984262408489059E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.5859262408489698E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.48774849912337E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.5172183951115414E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5.2327816048878262E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.3225979790653142E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.0395678750553259E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.3482199474590084</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.3152788872509857</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.4141020678750547</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.4388078630310712</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.4470431280830773</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.4470431280830773</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.2658672969389517</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.2411615017829343</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.3646904775630198</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2848-448F-8036-D93E901AC33F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2141612095"/>
+        <c:axId val="2141613055"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2141612095"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2141613055"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2141613055"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2141612095"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1059,7 +2396,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1136,10 +2473,10 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>'Voltage Divider'!$K$2:$K$17</c:f>
+              <c:f>'Voltage Divider'!$K$2:$K$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>300</c:v>
                 </c:pt>
@@ -1381,7 +2718,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1459,10 +2796,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'Voltage Divider'!$C$2:$C$26</c:f>
+              <c:f>'Voltage Divider'!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>25333.333333333332</c:v>
                 </c:pt>
@@ -1507,9 +2844,6 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>23822.222222222223</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25955.555555555551</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1549,10 +2883,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'Voltage Divider'!$F$2:$F$26</c:f>
+              <c:f>'Voltage Divider'!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>25033.333333333332</c:v>
                 </c:pt>
@@ -1597,9 +2931,6 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>23530.999999999996</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1812,7 +3143,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1890,10 +3221,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'Voltage Divider'!$J$2:$J$26</c:f>
+              <c:f>'Voltage Divider'!$J$2:$J$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>5.6250000000000355E-2</c:v>
                 </c:pt>
@@ -1938,9 +3269,6 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>5.4604166666667453E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1980,10 +3308,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'Voltage Divider'!$L$2:$L$26</c:f>
+              <c:f>'Voltage Divider'!$L$2:$L$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.5107964324865293E-4</c:v>
                 </c:pt>
@@ -2028,9 +3356,6 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>2.0395678750553259E-3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2403,6 +3728,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2920,7 +4365,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2947,8 +4392,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3028,6 +4473,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3038,6 +4488,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3049,7 +4504,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -3069,6 +4524,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3081,10 +4539,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -3124,23 +4582,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3245,8 +4702,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3378,20 +4835,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3405,17 +4861,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -3952,7 +5397,7 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3979,8 +5424,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -4060,11 +5505,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -4075,11 +5515,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -4091,7 +5526,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -4111,6 +5546,1048 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
@@ -4467,7 +6944,642 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>237877</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>136332</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>510209</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>107012</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A25CF0D0-3CDD-4CE2-91E1-6AA1903C6009}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>357477</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>20707</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>478885</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>19878</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57932F73-0718-4033-80DC-841C5D08A36F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>258417</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>43069</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>278295</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>3313</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{308D671A-0ED2-464A-94CD-87221EE991B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4508,7 +7620,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4622,6 +7734,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EADD3576-A8B4-4B81-91AD-519429F560D7}" name="Table43" displayName="Table43" ref="A1:M43" totalsRowShown="0">
+  <autoFilter ref="A1:M43" xr:uid="{C287309B-6D36-482C-AF41-B5EB3D643EA5}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{7376FCC2-8D1D-4C2E-8F7F-71AFBA16D09E}" name="Multimeter"/>
+    <tableColumn id="2" xr3:uid="{100E6936-6FC2-441A-89FF-8C459554B3A5}" name="Expected Divided Voltage" dataDxfId="10">
+      <calculatedColumnFormula>A2*$Q$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{D7EAD11B-454F-4329-A141-2734F6D6F2C2}" name="Expected Reading" dataDxfId="9">
+      <calculatedColumnFormula>B2/$Q$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{654308E6-1061-4B4F-A0BB-3DEACCC55197}" name="Sensor Voltage Reading"/>
+    <tableColumn id="5" xr3:uid="{910294DD-565C-4FF9-A5F7-3FACC93D02F7}" name="Actual Divided Voltage" dataDxfId="8">
+      <calculatedColumnFormula>D2*$Q$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{95FB3272-51CB-412E-956A-B132E278DB5B}" name="Actual ADC Reading" dataDxfId="7">
+      <calculatedColumnFormula>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{E28407D7-B350-49BF-B3AF-6C86EC78895B}" name="Full Voltage Difference " dataDxfId="6">
+      <calculatedColumnFormula>A2-D2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{0E03E051-C41B-460F-9503-A3393DAD91B4}" name="Adjusted Voltage" dataDxfId="5">
+      <calculatedColumnFormula>Table43[[#This Row],[Multimeter]]*$Q$9</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{BBC87D13-C3AC-4282-8D2F-4078806F8038}" name="Adjusted Reading" dataDxfId="4">
+      <calculatedColumnFormula>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{C35B8FD3-C8BC-43F3-B318-E3F269E03CD6}" name="Divided Voltage Difference" dataDxfId="3">
+      <calculatedColumnFormula>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{2327AD72-8F16-4BC6-AF43-5A3CD526D26F}" name="ADC Difference" dataDxfId="2">
+      <calculatedColumnFormula>C2-F2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{B5DD69B5-4173-4BDC-A5DA-A64F75D7A9D7}" name="Adjusted Voltage Difference" dataDxfId="1">
+      <calculatedColumnFormula>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{000A42A4-72B8-4DE2-BCC7-FE0CE15FF017}" name="Adjusted Reading Difference" dataDxfId="0">
+      <calculatedColumnFormula>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E6C1F1C-C346-40A2-AED4-01E548A5B84D}" name="Table1" displayName="Table1" ref="A1:G14" totalsRowShown="0">
   <autoFilter ref="A1:G14" xr:uid="{2E6C1F1C-C346-40A2-AED4-01E548A5B84D}"/>
   <tableColumns count="7">
@@ -4632,10 +7788,10 @@
     </tableColumn>
     <tableColumn id="4" xr3:uid="{0BFD2001-A65A-4633-88A3-5EE4BCD0BFA9}" name="Reading 1"/>
     <tableColumn id="5" xr3:uid="{A531ED5C-A85D-4EC7-8A8F-EB1246D50E06}" name="Reading 2"/>
-    <tableColumn id="6" xr3:uid="{071E4BEA-2A8E-4387-BCCA-C62120D9AA9E}" name="Reading Difference" dataDxfId="1">
+    <tableColumn id="6" xr3:uid="{071E4BEA-2A8E-4387-BCCA-C62120D9AA9E}" name="Reading Difference" dataDxfId="12">
       <calculatedColumnFormula>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A1F65FD6-F454-4AD6-8847-FBBE0F1435B6}" name="Column1" dataDxfId="0">
+    <tableColumn id="7" xr3:uid="{A1F65FD6-F454-4AD6-8847-FBBE0F1435B6}" name="Column1" dataDxfId="11">
       <calculatedColumnFormula>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4643,43 +7799,43 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C287309B-6D36-482C-AF41-B5EB3D643EA5}" name="Table4" displayName="Table4" ref="A1:M17" totalsRowShown="0">
-  <autoFilter ref="A1:M17" xr:uid="{C287309B-6D36-482C-AF41-B5EB3D643EA5}"/>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C287309B-6D36-482C-AF41-B5EB3D643EA5}" name="Table4" displayName="Table4" ref="A1:M16" totalsRowShown="0">
+  <autoFilter ref="A1:M16" xr:uid="{C287309B-6D36-482C-AF41-B5EB3D643EA5}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{18D4E79D-61C4-4283-8EA8-0C486CCB9C95}" name="Multimeter"/>
-    <tableColumn id="2" xr3:uid="{3D3DDF7A-B91C-4E0F-938B-9BAF2BF8E62D}" name="Expected Divided Voltage" dataDxfId="12">
+    <tableColumn id="2" xr3:uid="{3D3DDF7A-B91C-4E0F-938B-9BAF2BF8E62D}" name="Expected Divided Voltage" dataDxfId="23">
       <calculatedColumnFormula>A2*$Q$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0F13E274-0523-4466-A526-31E85B78F146}" name="Expected Reading" dataDxfId="11">
+    <tableColumn id="3" xr3:uid="{0F13E274-0523-4466-A526-31E85B78F146}" name="Expected Reading" dataDxfId="22">
       <calculatedColumnFormula>B2/$Q$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{4CCC83DC-22C2-4736-A10B-B38C77E7337F}" name="Sensor Voltage Reading"/>
-    <tableColumn id="5" xr3:uid="{285047F7-9E22-4A5B-97BE-8FBEAD0648C1}" name="Actual Divided Voltage" dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{285047F7-9E22-4A5B-97BE-8FBEAD0648C1}" name="Actual Divided Voltage" dataDxfId="21">
       <calculatedColumnFormula>D2*$Q$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3F79C850-08A4-4F6B-BCA8-9B58B3875326}" name="Actual ADC Reading" dataDxfId="9">
+    <tableColumn id="6" xr3:uid="{3F79C850-08A4-4F6B-BCA8-9B58B3875326}" name="Actual ADC Reading" dataDxfId="20">
       <calculatedColumnFormula>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{68302041-C69D-433E-A989-FCEC783376DE}" name="Full Voltage Difference " dataDxfId="8">
+    <tableColumn id="7" xr3:uid="{68302041-C69D-433E-A989-FCEC783376DE}" name="Full Voltage Difference " dataDxfId="19">
       <calculatedColumnFormula>A2-D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E64556C4-E822-4B9E-A72A-A68BEF816C34}" name="Adjusted Voltage" dataDxfId="7">
+    <tableColumn id="13" xr3:uid="{E64556C4-E822-4B9E-A72A-A68BEF816C34}" name="Adjusted Voltage" dataDxfId="18">
       <calculatedColumnFormula>Table4[[#This Row],[Multimeter]]*$Q$9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8286CDF6-5417-4249-B41A-4CB5D0435F96}" name="Adjusted Reading" dataDxfId="6">
+    <tableColumn id="10" xr3:uid="{8286CDF6-5417-4249-B41A-4CB5D0435F96}" name="Adjusted Reading" dataDxfId="17">
       <calculatedColumnFormula>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{3DEF19D2-003D-49E5-A953-97D2E6AFE232}" name="Divided Voltage Difference" dataDxfId="5">
+    <tableColumn id="8" xr3:uid="{3DEF19D2-003D-49E5-A953-97D2E6AFE232}" name="Divided Voltage Difference" dataDxfId="16">
       <calculatedColumnFormula>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6EC4AB3F-3B02-4418-9131-0736232C7684}" name="ADC Difference" dataDxfId="4">
+    <tableColumn id="9" xr3:uid="{6EC4AB3F-3B02-4418-9131-0736232C7684}" name="ADC Difference" dataDxfId="15">
       <calculatedColumnFormula>C2-F2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{41706AD2-D388-4A38-AF4E-437961598AA7}" name="Adjusted Voltage Difference" dataDxfId="3">
+    <tableColumn id="14" xr3:uid="{41706AD2-D388-4A38-AF4E-437961598AA7}" name="Adjusted Voltage Difference" dataDxfId="14">
       <calculatedColumnFormula>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{246ABA43-71F5-431B-999E-412B2AD3C38D}" name="Adjusted Reading Difference" dataDxfId="2">
+    <tableColumn id="12" xr3:uid="{246ABA43-71F5-431B-999E-412B2AD3C38D}" name="Adjusted Reading Difference" dataDxfId="13">
       <calculatedColumnFormula>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5003,1089 +8159,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDD4075C-118D-4BC9-9E59-C74B697F8432}">
-  <dimension ref="A1:P50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="5" width="10.88671875" customWidth="1"/>
-    <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B2">
-        <v>25.2</v>
-      </c>
-      <c r="C2">
-        <f>B2/A2</f>
-        <v>22.909090909090907</v>
-      </c>
-      <c r="D2">
-        <v>6062</v>
-      </c>
-      <c r="E2">
-        <v>6067</v>
-      </c>
-      <c r="F2">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>8.2413054227789675E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>24.8</v>
-      </c>
-      <c r="C3">
-        <f t="shared" ref="C3:C9" si="0">B3/A3</f>
-        <v>24.8</v>
-      </c>
-      <c r="D3">
-        <v>6846</v>
-      </c>
-      <c r="E3">
-        <v>6999</v>
-      </c>
-      <c r="F3">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>153</v>
-      </c>
-      <c r="G3">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>2.1860265752250321</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>25.1</v>
-      </c>
-      <c r="C4">
-        <f t="shared" si="0"/>
-        <v>25.1</v>
-      </c>
-      <c r="D4">
-        <v>7610</v>
-      </c>
-      <c r="E4">
-        <v>7777</v>
-      </c>
-      <c r="F4">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>167</v>
-      </c>
-      <c r="G4">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>2.1473575929021473</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1.3</v>
-      </c>
-      <c r="B5">
-        <v>25.3</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="0"/>
-        <v>19.46153846153846</v>
-      </c>
-      <c r="D5">
-        <v>6160</v>
-      </c>
-      <c r="E5">
-        <v>6305</v>
-      </c>
-      <c r="F5">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>145</v>
-      </c>
-      <c r="G5">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>2.2997620935765264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B6">
-        <v>24.8</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>22.545454545454543</v>
-      </c>
-      <c r="D6">
-        <v>8584</v>
-      </c>
-      <c r="E6">
-        <v>8761</v>
-      </c>
-      <c r="F6">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>177</v>
-      </c>
-      <c r="G6">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>2.0203173153749572</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>0.8</v>
-      </c>
-      <c r="B7">
-        <v>24.5</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>30.625</v>
-      </c>
-      <c r="D7">
-        <v>10995</v>
-      </c>
-      <c r="E7">
-        <v>11197</v>
-      </c>
-      <c r="F7">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>202</v>
-      </c>
-      <c r="G7">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>1.804054657497544</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>0.8</v>
-      </c>
-      <c r="B8">
-        <v>24.3</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>30.375</v>
-      </c>
-      <c r="D8">
-        <v>11514</v>
-      </c>
-      <c r="E8">
-        <v>11735</v>
-      </c>
-      <c r="F8">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>221</v>
-      </c>
-      <c r="G8">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>1.8832552194290584</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>0.8</v>
-      </c>
-      <c r="B9">
-        <v>24.5</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>30.625</v>
-      </c>
-      <c r="D9">
-        <v>11397</v>
-      </c>
-      <c r="E9">
-        <v>11609</v>
-      </c>
-      <c r="F9">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>212</v>
-      </c>
-      <c r="G9">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>1.8261693513653201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>25.1</v>
-      </c>
-      <c r="C10">
-        <f>B10/A10</f>
-        <v>25.1</v>
-      </c>
-      <c r="D10">
-        <v>7392</v>
-      </c>
-      <c r="E10">
-        <v>7548</v>
-      </c>
-      <c r="F10">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>156</v>
-      </c>
-      <c r="G10">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>2.066772655007949</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>25.3</v>
-      </c>
-      <c r="C11">
-        <f>B11/A11</f>
-        <v>25.3</v>
-      </c>
-      <c r="D11">
-        <v>6535</v>
-      </c>
-      <c r="E11">
-        <v>6696</v>
-      </c>
-      <c r="F11">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>161</v>
-      </c>
-      <c r="G11">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>2.40442054958184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B12">
-        <v>25.4</v>
-      </c>
-      <c r="C12">
-        <f>B12/A12</f>
-        <v>23.090909090909086</v>
-      </c>
-      <c r="D12">
-        <v>6039</v>
-      </c>
-      <c r="E12">
-        <v>6188</v>
-      </c>
-      <c r="F12">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>149</v>
-      </c>
-      <c r="G12">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>2.4078862314156431</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>-57</v>
-      </c>
-      <c r="E13">
-        <v>-22</v>
-      </c>
-      <c r="F13">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>35</v>
-      </c>
-      <c r="G13">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>-159.09090909090909</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C14">
-        <v>100</v>
-      </c>
-      <c r="D14">
-        <f>5/0.0001875</f>
-        <v>26666.666666666668</v>
-      </c>
-      <c r="E14" s="11">
-        <f>5/0.0001875</f>
-        <v>26666.666666666668</v>
-      </c>
-      <c r="F14" s="14">
-        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="7">
-        <v>80</v>
-      </c>
-      <c r="N21" s="11"/>
-      <c r="O21" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H22" s="11"/>
-      <c r="I22" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="P22" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H23" s="11"/>
-      <c r="I23" s="13">
-        <v>363.17</v>
-      </c>
-      <c r="J23" s="13">
-        <v>-898.46</v>
-      </c>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13">
-        <f>IF(ISNUMBER(I23),$I23*M$21+$J23,"")</f>
-        <v>28155.140000000003</v>
-      </c>
-      <c r="M23" s="13">
-        <f>IF(ISNUMBER(I23),L23/(80000/3)*100,"")</f>
-        <v>105.58177500000001</v>
-      </c>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13">
-        <f>IF(ISNUMBER(I23),$I23*P$21+$J23, "")</f>
-        <v>17260.04</v>
-      </c>
-      <c r="P23" s="13">
-        <f>IF(ISNUMBER(I23),O23/(80000/3)*100, "")</f>
-        <v>64.725149999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H24" s="11"/>
-      <c r="I24" s="11">
-        <v>257.27999999999997</v>
-      </c>
-      <c r="J24" s="11">
-        <v>1087.0999999999999</v>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11">
-        <f t="shared" ref="L24:L53" si="1">IF(ISNUMBER(I24),$I24*M$21+$J24,"")</f>
-        <v>21669.499999999996</v>
-      </c>
-      <c r="M24" s="11">
-        <f t="shared" ref="M24:M52" si="2">IF(ISNUMBER(I24),L24/(80000/3)*100,"")</f>
-        <v>81.26062499999999</v>
-      </c>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11">
-        <f t="shared" ref="O24:O52" si="3">IF(ISNUMBER(I24),$I24*P$21+$J24, "")</f>
-        <v>13951.099999999999</v>
-      </c>
-      <c r="P24" s="11">
-        <f t="shared" ref="P24:P51" si="4">IF(ISNUMBER(I24),O24/(80000/3)*100, "")</f>
-        <v>52.316624999999995</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="B25" s="2">
-        <v>25</v>
-      </c>
-      <c r="C25" s="2">
-        <f>B25/A25</f>
-        <v>41.666666666666671</v>
-      </c>
-      <c r="D25" s="2">
-        <v>8844</v>
-      </c>
-      <c r="E25" s="3">
-        <v>9005</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" s="13">
-        <v>363.88</v>
-      </c>
-      <c r="J25" s="13">
-        <v>-916.73</v>
-      </c>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13">
-        <f t="shared" si="1"/>
-        <v>28193.670000000002</v>
-      </c>
-      <c r="M25" s="13">
-        <f t="shared" si="2"/>
-        <v>105.72626250000002</v>
-      </c>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13">
-        <f t="shared" si="3"/>
-        <v>17277.27</v>
-      </c>
-      <c r="P25" s="13">
-        <f t="shared" si="4"/>
-        <v>64.789762500000009</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="B26" s="2">
-        <v>25.5</v>
-      </c>
-      <c r="C26" s="2">
-        <f>B26/A26</f>
-        <v>31.875</v>
-      </c>
-      <c r="D26" s="2">
-        <v>6136</v>
-      </c>
-      <c r="E26" s="3">
-        <v>6276</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I26" s="11">
-        <v>328.52</v>
-      </c>
-      <c r="J26" s="11">
-        <v>0</v>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11">
-        <f t="shared" si="1"/>
-        <v>26281.599999999999</v>
-      </c>
-      <c r="M26" s="11">
-        <f t="shared" si="2"/>
-        <v>98.555999999999983</v>
-      </c>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11">
-        <f t="shared" si="3"/>
-        <v>16426</v>
-      </c>
-      <c r="P26" s="11">
-        <f t="shared" si="4"/>
-        <v>61.597499999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H27" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I27" s="13">
-        <v>363.17</v>
-      </c>
-      <c r="J27" s="13">
-        <v>-898.46</v>
-      </c>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13">
-        <f t="shared" si="1"/>
-        <v>28155.140000000003</v>
-      </c>
-      <c r="M27" s="13">
-        <f t="shared" si="2"/>
-        <v>105.58177500000001</v>
-      </c>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13">
-        <f t="shared" si="3"/>
-        <v>17260.04</v>
-      </c>
-      <c r="P27" s="13">
-        <f t="shared" si="4"/>
-        <v>64.725149999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H28" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I28" s="11">
-        <v>262.64</v>
-      </c>
-      <c r="J28" s="11">
-        <v>1364.8</v>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11">
-        <f t="shared" si="1"/>
-        <v>22375.999999999996</v>
-      </c>
-      <c r="M28" s="11">
-        <f t="shared" si="2"/>
-        <v>83.909999999999982</v>
-      </c>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11">
-        <f t="shared" si="3"/>
-        <v>14496.8</v>
-      </c>
-      <c r="P28" s="11">
-        <f t="shared" si="4"/>
-        <v>54.362999999999992</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M29" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P29" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M30" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P30" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H31" s="11"/>
-      <c r="I31" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M31" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P31" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H32" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I32" s="13">
-        <v>385.19</v>
-      </c>
-      <c r="J32" s="13">
-        <v>-932.7</v>
-      </c>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13">
-        <f t="shared" si="1"/>
-        <v>29882.5</v>
-      </c>
-      <c r="M32" s="13">
-        <f t="shared" si="2"/>
-        <v>112.059375</v>
-      </c>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13">
-        <f t="shared" si="3"/>
-        <v>18326.8</v>
-      </c>
-      <c r="P32" s="13">
-        <f t="shared" si="4"/>
-        <v>68.725499999999997</v>
-      </c>
-    </row>
-    <row r="33" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="H33" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I33" s="11">
-        <v>322.22000000000003</v>
-      </c>
-      <c r="J33" s="11">
-        <v>0</v>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11">
-        <f t="shared" si="1"/>
-        <v>25777.600000000002</v>
-      </c>
-      <c r="M33" s="11">
-        <f t="shared" si="2"/>
-        <v>96.666000000000011</v>
-      </c>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11">
-        <f t="shared" si="3"/>
-        <v>16111.000000000002</v>
-      </c>
-      <c r="P33" s="11">
-        <f t="shared" si="4"/>
-        <v>60.416250000000005</v>
-      </c>
-    </row>
-    <row r="34" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="H34" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I34" s="13">
-        <v>356.37</v>
-      </c>
-      <c r="J34" s="13">
-        <v>-885.38</v>
-      </c>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13">
-        <f t="shared" si="1"/>
-        <v>27624.219999999998</v>
-      </c>
-      <c r="M34" s="13">
-        <f t="shared" si="2"/>
-        <v>103.59082499999998</v>
-      </c>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13">
-        <f t="shared" si="3"/>
-        <v>16933.12</v>
-      </c>
-      <c r="P34" s="13">
-        <f t="shared" si="4"/>
-        <v>63.499199999999988</v>
-      </c>
-    </row>
-    <row r="35" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="H35" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I35" s="11">
-        <v>263.67</v>
-      </c>
-      <c r="J35" s="11">
-        <v>1197.4000000000001</v>
-      </c>
-      <c r="L35">
-        <f t="shared" si="1"/>
-        <v>22291.000000000004</v>
-      </c>
-      <c r="M35">
-        <f t="shared" si="2"/>
-        <v>83.591250000000002</v>
-      </c>
-      <c r="O35">
-        <f t="shared" si="3"/>
-        <v>14380.9</v>
-      </c>
-      <c r="P35">
-        <f t="shared" si="4"/>
-        <v>53.928374999999996</v>
-      </c>
-    </row>
-    <row r="36" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="L36" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M36" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O36" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P36" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L37" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M37" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O37" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P37" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L38" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M38" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O38" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P38" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L39" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M39" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O39" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P39" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L40" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M40" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L41" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O41" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P41" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L42" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M42" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O42" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P42" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L43" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M43" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O43" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P43" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L44" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M44" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O44" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P44" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L45" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M45" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O45" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P45" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L46" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M46" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O46" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P46" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L47" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M47" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O47" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P47" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="L48" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M48" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O48" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P48" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="12:16" x14ac:dyDescent="0.3">
-      <c r="L49" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M49" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O49" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P49" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="12:16" x14ac:dyDescent="0.3">
-      <c r="L50" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M50" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O50" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P50" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC7156C4-D780-4AF4-81FE-0216F154F497}">
-  <dimension ref="A1:U26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{792FBFF7-1228-41CC-BBDF-177DFC971997}">
+  <dimension ref="A1:U43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -6146,12 +8221,12 @@
         <v>29</v>
       </c>
       <c r="M1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="10"/>
+      <c r="Q1" s="11"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
@@ -6173,7 +8248,7 @@
         <v>4.6937499999999996</v>
       </c>
       <c r="F2">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>25033.333333333332</v>
       </c>
       <c r="G2">
@@ -6181,15 +8256,15 @@
         <v>0.67499999999999716</v>
       </c>
       <c r="H2">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.6941010796432483</v>
       </c>
       <c r="I2">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>24746.205758097323</v>
       </c>
       <c r="J2">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.6250000000000355E-2</v>
       </c>
       <c r="K2">
@@ -6197,17 +8272,17 @@
         <v>300</v>
       </c>
       <c r="L2">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>3.5107964324865293E-4</v>
       </c>
       <c r="M2">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-287.12757523600885</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="7">
         <v>1.875E-4</v>
       </c>
     </row>
@@ -6231,7 +8306,7 @@
         <v>4.6342499999999998</v>
       </c>
       <c r="F3">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24716</v>
       </c>
       <c r="G3">
@@ -6239,15 +8314,15 @@
         <v>0.68900000000000006</v>
       </c>
       <c r="H3">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.6364542242792082</v>
       </c>
       <c r="I3">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>24438.755862822443</v>
       </c>
       <c r="J3">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.7416666666666671E-2</v>
       </c>
       <c r="K3">
@@ -6255,17 +8330,17 @@
         <v>306.22222222221899</v>
       </c>
       <c r="L3">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>2.204224279208411E-3</v>
       </c>
       <c r="M3">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-277.24413717755669</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="6">
         <v>110</v>
       </c>
     </row>
@@ -6289,7 +8364,7 @@
         <v>4.6353749999999998</v>
       </c>
       <c r="F4">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24722</v>
       </c>
       <c r="G4">
@@ -6297,15 +8372,15 @@
         <v>0.67549999999999955</v>
       </c>
       <c r="H4">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.6364542242792082</v>
       </c>
       <c r="I4">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>24438.755862822443</v>
       </c>
       <c r="J4">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.6291666666666629E-2</v>
       </c>
       <c r="K4">
@@ -6313,17 +8388,17 @@
         <v>300.22222222221899</v>
       </c>
       <c r="L4">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>1.0792242792083684E-3</v>
       </c>
       <c r="M4">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-283.24413717755669</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="6">
         <v>10</v>
       </c>
     </row>
@@ -6347,7 +8422,7 @@
         <v>4.6297499999999996</v>
       </c>
       <c r="F5">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24691.999999999996</v>
       </c>
       <c r="G5">
@@ -6355,15 +8430,15 @@
         <v>0.64300000000000068</v>
       </c>
       <c r="H5">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.6282189592272029</v>
       </c>
       <c r="I5">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>24394.83444921175</v>
       </c>
       <c r="J5">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.3583333333333982E-2</v>
       </c>
       <c r="K5">
@@ -6371,17 +8446,17 @@
         <v>285.77777777778101</v>
       </c>
       <c r="L5">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>-1.5310407727966435E-3</v>
       </c>
       <c r="M5">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-297.16555078824604</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="Q5" s="6">
         <f>Q4/(Q4+Q3)</f>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -6406,7 +8481,7 @@
         <v>4.6321874999999997</v>
       </c>
       <c r="F6">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24704.999999999996</v>
       </c>
       <c r="G6">
@@ -6414,15 +8489,15 @@
         <v>0.61375000000000313</v>
       </c>
       <c r="H6">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.6282189592272029</v>
       </c>
       <c r="I6">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>24394.83444921175</v>
       </c>
       <c r="J6">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.114583333333389E-2</v>
       </c>
       <c r="K6">
@@ -6430,11 +8505,11 @@
         <v>272.77777777778101</v>
       </c>
       <c r="L6">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>-3.9685407727967359E-3</v>
       </c>
       <c r="M6">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-310.16555078824604</v>
       </c>
     </row>
@@ -6458,7 +8533,7 @@
         <v>4.5912499999999996</v>
       </c>
       <c r="F7">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24486.666666666664</v>
       </c>
       <c r="G7">
@@ -6466,15 +8541,15 @@
         <v>0.70499999999999829</v>
       </c>
       <c r="H7">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.5952778990191794</v>
       </c>
       <c r="I7">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>24219.148794768957</v>
       </c>
       <c r="J7">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.8749999999999858E-2</v>
       </c>
       <c r="K7">
@@ -6482,21 +8557,21 @@
         <v>313.33333333333212</v>
       </c>
       <c r="L7">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>4.0278990191797703E-3</v>
       </c>
       <c r="M7">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-267.51787189770766</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="Q7" s="6">
         <v>111429</v>
       </c>
       <c r="R7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
@@ -6519,7 +8594,7 @@
         <v>4.57</v>
       </c>
       <c r="F8">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24373.333333333336</v>
       </c>
       <c r="G8">
@@ -6527,15 +8602,15 @@
         <v>0.55999999999999517</v>
       </c>
       <c r="H8">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.5623368388111567</v>
       </c>
       <c r="I8">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>24043.46314032617</v>
       </c>
       <c r="J8">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>4.6666666666665968E-2</v>
       </c>
       <c r="K8">
@@ -6543,17 +8618,17 @@
         <v>248.88888888888323</v>
       </c>
       <c r="L8">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>-7.6631611888435813E-3</v>
       </c>
       <c r="M8">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-329.87019300716565</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="Q8" s="6">
         <v>10000</v>
       </c>
     </row>
@@ -6577,7 +8652,7 @@
         <v>4.5534374999999994</v>
       </c>
       <c r="F9">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24284.999999999996</v>
       </c>
       <c r="G9">
@@ -6585,15 +8660,15 @@
         <v>0.65874999999999773</v>
       </c>
       <c r="H9">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.5541015737591506</v>
       </c>
       <c r="I9">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>23999.54172671547</v>
       </c>
       <c r="J9">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.4895833333333144E-2</v>
       </c>
       <c r="K9">
@@ -6601,21 +8676,21 @@
         <v>292.77777777777737</v>
       </c>
       <c r="L9">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>6.6407375915122913E-4</v>
       </c>
       <c r="M9">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-285.45827328452651</v>
       </c>
-      <c r="P9" s="7" t="s">
-        <v>35</v>
+      <c r="P9" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="Q9">
         <f>Q8/(Q8+Q7)</f>
         <v>8.2352650520056983E-2</v>
       </c>
-      <c r="R9" s="7">
+      <c r="R9" s="6">
         <v>8.2352999999999996E-2</v>
       </c>
     </row>
@@ -6639,7 +8714,7 @@
         <v>4.5569999999999995</v>
       </c>
       <c r="F10">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24303.999999999996</v>
       </c>
       <c r="G10">
@@ -6647,15 +8722,15 @@
         <v>0.61599999999999966</v>
       </c>
       <c r="H10">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.5541015737591506</v>
       </c>
       <c r="I10">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>23999.54172671547</v>
       </c>
       <c r="J10">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.1333333333333009E-2</v>
       </c>
       <c r="K10">
@@ -6663,21 +8738,21 @@
         <v>273.77777777777737</v>
       </c>
       <c r="L10">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>-2.8984262408489059E-3</v>
       </c>
       <c r="M10">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-304.45827328452651</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q10" s="6">
         <v>-289</v>
       </c>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -6699,7 +8774,7 @@
         <v>4.5586874999999996</v>
       </c>
       <c r="F11">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24312.999999999996</v>
       </c>
       <c r="G11">
@@ -6707,15 +8782,15 @@
         <v>0.59574999999999534</v>
       </c>
       <c r="H11">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.5541015737591506</v>
       </c>
       <c r="I11">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>23999.54172671547</v>
       </c>
       <c r="J11">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>4.9645833333332945E-2</v>
       </c>
       <c r="K11">
@@ -6723,11 +8798,11 @@
         <v>264.77777777777737</v>
       </c>
       <c r="L11">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>-4.5859262408489698E-3</v>
       </c>
       <c r="M11">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-313.45827328452651</v>
       </c>
     </row>
@@ -6751,7 +8826,7 @@
         <v>4.5054374999999993</v>
       </c>
       <c r="F12">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24028.999999999996</v>
       </c>
       <c r="G12">
@@ -6759,15 +8834,15 @@
         <v>0.73474999999999824</v>
       </c>
       <c r="H12">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.5129252484991227</v>
       </c>
       <c r="I12">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>23779.934658661987</v>
       </c>
       <c r="J12">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>6.1229166666667112E-2</v>
       </c>
       <c r="K12">
@@ -6775,11 +8850,11 @@
         <v>326.55555555555839</v>
       </c>
       <c r="L12">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>7.48774849912337E-3</v>
       </c>
       <c r="M12">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-249.0653413380096</v>
       </c>
     </row>
@@ -6803,7 +8878,7 @@
         <v>4.4949374999999998</v>
       </c>
       <c r="F13">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>23973</v>
       </c>
       <c r="G13">
@@ -6811,15 +8886,15 @@
         <v>0.66075000000000017</v>
       </c>
       <c r="H13">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.4964547183951113</v>
       </c>
       <c r="I13">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>23692.091831440594</v>
       </c>
       <c r="J13">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.5062500000000014E-2</v>
       </c>
       <c r="K13">
@@ -6827,19 +8902,19 @@
         <v>293.66666666666424</v>
       </c>
       <c r="L13">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>1.5172183951115414E-3</v>
       </c>
       <c r="M13">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-280.90816855940648</v>
       </c>
-      <c r="P13" s="7" t="s">
+      <c r="P13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="Q13" s="7">
-        <f>AVERAGE(Table4[Adjusted Voltage Difference])</f>
-        <v>-1.2416206178045287E-5</v>
+      <c r="Q13" s="6">
+        <f>AVERAGE(Table43[Adjusted Voltage Difference])</f>
+        <v>2.7124105614437135</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
@@ -6862,7 +8937,7 @@
         <v>4.5016874999999992</v>
       </c>
       <c r="F14">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>24008.999999999996</v>
       </c>
       <c r="G14">
@@ -6870,15 +8945,15 @@
         <v>0.57975000000000421</v>
       </c>
       <c r="H14">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.4964547183951113</v>
       </c>
       <c r="I14">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>23692.091831440594</v>
       </c>
       <c r="J14">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>4.8312500000000647E-2</v>
       </c>
       <c r="K14">
@@ -6886,19 +8961,19 @@
         <v>257.66666666666788</v>
       </c>
       <c r="L14">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>-5.2327816048878262E-3</v>
       </c>
       <c r="M14">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-316.90816855940284</v>
       </c>
-      <c r="P14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q14" s="7">
-        <f>AVERAGE(Table4[Adjusted Reading Difference])</f>
-        <v>-289.06621976628304</v>
+      <c r="P14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14" s="6">
+        <f>AVERAGE(Table43[Adjusted Reading Difference])</f>
+        <v>-278.51765604002958</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
@@ -6921,7 +8996,7 @@
         <v>4.4242499999999998</v>
       </c>
       <c r="F15">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>23596</v>
       </c>
       <c r="G15">
@@ -6929,15 +9004,15 @@
         <v>0.70899999999999608</v>
       </c>
       <c r="H15">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.4305725979790651</v>
       </c>
       <c r="I15">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
         <v>23340.720522555013</v>
       </c>
       <c r="J15">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>5.908333333333271E-2</v>
       </c>
       <c r="K15">
@@ -6945,11 +9020,11 @@
         <v>315.11111111110586</v>
       </c>
       <c r="L15">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
         <v>6.3225979790653142E-3</v>
       </c>
       <c r="M15">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
         <v>-255.2794774449867</v>
       </c>
     </row>
@@ -6973,7 +9048,7 @@
         <v>4.4120624999999993</v>
       </c>
       <c r="F16">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <f>Table43[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
         <v>23530.999999999996</v>
       </c>
       <c r="G16">
@@ -6981,6 +9056,3020 @@
         <v>0.65525000000000233</v>
       </c>
       <c r="H16">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.4141020678750547</v>
+      </c>
+      <c r="I16">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23252.877695333624</v>
+      </c>
+      <c r="J16">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.4604166666667453E-2</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="4"/>
+        <v>291.22222222222626</v>
+      </c>
+      <c r="L16">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>2.0395678750553259E-3</v>
+      </c>
+      <c r="M16">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-278.12230466637266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="15">
+        <v>55.2</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="12">
+        <v>24273</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
+        <v>52.8</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12">
+        <v>23145</v>
+      </c>
+      <c r="G18" s="12">
+        <f t="shared" ref="G18:G43" si="5">A18-D18</f>
+        <v>52.8</v>
+      </c>
+      <c r="H18" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.3482199474590084</v>
+      </c>
+      <c r="I18" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22901.506386448043</v>
+      </c>
+      <c r="J18" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="12" t="e">
+        <f>C18-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L18" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.3482199474590084</v>
+      </c>
+      <c r="M18" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-243.49361355195651</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
+        <v>52.4</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12">
+        <v>22989</v>
+      </c>
+      <c r="G19" s="12">
+        <f t="shared" si="5"/>
+        <v>52.4</v>
+      </c>
+      <c r="H19" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.3152788872509857</v>
+      </c>
+      <c r="I19" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22725.820732005257</v>
+      </c>
+      <c r="J19" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="12" t="e">
+        <f>C19-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L19" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.3152788872509857</v>
+      </c>
+      <c r="M19" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-263.17926799474299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="12">
+        <v>53.6</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12">
+        <v>23524</v>
+      </c>
+      <c r="G20" s="12">
+        <f t="shared" si="5"/>
+        <v>53.6</v>
+      </c>
+      <c r="H20" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.4141020678750547</v>
+      </c>
+      <c r="I20" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23252.877695333624</v>
+      </c>
+      <c r="J20" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="12" t="e">
+        <f>C20-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L20" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.4141020678750547</v>
+      </c>
+      <c r="M20" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-271.12230466637629</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
+        <v>53.9</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12">
+        <v>23690</v>
+      </c>
+      <c r="G21" s="12">
+        <f t="shared" si="5"/>
+        <v>53.9</v>
+      </c>
+      <c r="H21" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.4388078630310712</v>
+      </c>
+      <c r="I21" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23384.641936165714</v>
+      </c>
+      <c r="J21" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="12" t="e">
+        <f>C21-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L21" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.4388078630310712</v>
+      </c>
+      <c r="M21" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-305.35806383428644</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
+        <v>54</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12">
+        <v>23710</v>
+      </c>
+      <c r="G22" s="12">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="H22" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.4470431280830773</v>
+      </c>
+      <c r="I22" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23428.56334977641</v>
+      </c>
+      <c r="J22" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="12" t="e">
+        <f>C22-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L22" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.4470431280830773</v>
+      </c>
+      <c r="M22" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-281.43665022358982</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
+        <v>54</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12">
+        <v>23738</v>
+      </c>
+      <c r="G23" s="12">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="H23" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.4470431280830773</v>
+      </c>
+      <c r="I23" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23428.56334977641</v>
+      </c>
+      <c r="J23" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="12" t="e">
+        <f>C23-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L23" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.4470431280830773</v>
+      </c>
+      <c r="M23" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-309.43665022358982</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="12">
+        <v>51.8</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12">
+        <v>22720</v>
+      </c>
+      <c r="G24" s="12">
+        <f t="shared" si="5"/>
+        <v>51.8</v>
+      </c>
+      <c r="H24" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.2658672969389517</v>
+      </c>
+      <c r="I24" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22462.292250341074</v>
+      </c>
+      <c r="J24" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="12" t="e">
+        <f>C24-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L24" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.2658672969389517</v>
+      </c>
+      <c r="M24" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-257.70774965892633</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="12">
+        <v>51.5</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12">
+        <v>22609</v>
+      </c>
+      <c r="G25" s="12">
+        <f t="shared" si="5"/>
+        <v>51.5</v>
+      </c>
+      <c r="H25" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.2411615017829343</v>
+      </c>
+      <c r="I25" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22330.528009508984</v>
+      </c>
+      <c r="J25" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="12" t="e">
+        <f>C25-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L25" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.2411615017829343</v>
+      </c>
+      <c r="M25" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-278.47199049101619</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="16">
+        <v>53</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13">
+        <v>23276</v>
+      </c>
+      <c r="G26" s="13">
+        <f t="shared" si="5"/>
+        <v>53</v>
+      </c>
+      <c r="H26" s="13">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.3646904775630198</v>
+      </c>
+      <c r="I26" s="13">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22989.349213669437</v>
+      </c>
+      <c r="J26" s="13">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="13" t="e">
+        <f>C26-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L26" s="13">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.3646904775630198</v>
+      </c>
+      <c r="M26" s="14">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-286.65078633056328</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="12">
+        <v>53.1</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12">
+        <v>23302</v>
+      </c>
+      <c r="G27" s="12">
+        <f t="shared" si="5"/>
+        <v>53.1</v>
+      </c>
+      <c r="H27" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.3729257426150259</v>
+      </c>
+      <c r="I27" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23033.270627280137</v>
+      </c>
+      <c r="J27" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="12" t="e">
+        <f>C27-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L27" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.3729257426150259</v>
+      </c>
+      <c r="M27" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-268.72937271986302</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
+        <v>53.1</v>
+      </c>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12">
+        <v>23311</v>
+      </c>
+      <c r="G28" s="12">
+        <f t="shared" si="5"/>
+        <v>53.1</v>
+      </c>
+      <c r="H28" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.3729257426150259</v>
+      </c>
+      <c r="I28" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23033.270627280137</v>
+      </c>
+      <c r="J28" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="12" t="e">
+        <f>C28-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L28" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.3729257426150259</v>
+      </c>
+      <c r="M28" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-277.72937271986302</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
+        <v>50.9</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12">
+        <v>22354</v>
+      </c>
+      <c r="G29" s="12">
+        <f t="shared" si="5"/>
+        <v>50.9</v>
+      </c>
+      <c r="H29" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.1917499114709003</v>
+      </c>
+      <c r="I29" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22066.9995278448</v>
+      </c>
+      <c r="J29" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="12" t="e">
+        <f>C29-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L29" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.1917499114709003</v>
+      </c>
+      <c r="M29" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-287.00047215519953</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="12">
+        <v>52.1</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12">
+        <v>22817</v>
+      </c>
+      <c r="G30" s="12">
+        <f t="shared" si="5"/>
+        <v>52.1</v>
+      </c>
+      <c r="H30" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.2905730920949692</v>
+      </c>
+      <c r="I30" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22594.056491173167</v>
+      </c>
+      <c r="J30" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="12" t="e">
+        <f>C30-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L30" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.2905730920949692</v>
+      </c>
+      <c r="M30" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-222.94350882683284</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="12">
+        <v>52.3</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12">
+        <v>22974</v>
+      </c>
+      <c r="G31" s="12">
+        <f t="shared" si="5"/>
+        <v>52.3</v>
+      </c>
+      <c r="H31" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.3070436221989796</v>
+      </c>
+      <c r="I31" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22681.899318394557</v>
+      </c>
+      <c r="J31" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="12" t="e">
+        <f>C31-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L31" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.3070436221989796</v>
+      </c>
+      <c r="M31" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-292.10068160544324</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="12">
+        <v>52.4</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12">
+        <v>22988</v>
+      </c>
+      <c r="G32" s="12">
+        <f t="shared" si="5"/>
+        <v>52.4</v>
+      </c>
+      <c r="H32" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.3152788872509857</v>
+      </c>
+      <c r="I32" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22725.820732005257</v>
+      </c>
+      <c r="J32" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="12" t="e">
+        <f>C32-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L32" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.3152788872509857</v>
+      </c>
+      <c r="M32" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-262.17926799474299</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="12">
+        <v>50.9</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12">
+        <v>22329</v>
+      </c>
+      <c r="G33" s="12">
+        <f t="shared" si="5"/>
+        <v>50.9</v>
+      </c>
+      <c r="H33" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.1917499114709003</v>
+      </c>
+      <c r="I33" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22066.9995278448</v>
+      </c>
+      <c r="J33" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="12" t="e">
+        <f>C33-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L33" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.1917499114709003</v>
+      </c>
+      <c r="M33" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-262.00047215519953</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="12">
+        <v>50.4</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12">
+        <v>22107</v>
+      </c>
+      <c r="G34" s="12">
+        <f t="shared" si="5"/>
+        <v>50.4</v>
+      </c>
+      <c r="H34" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.1505735862108715</v>
+      </c>
+      <c r="I34" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>21847.392459791314</v>
+      </c>
+      <c r="J34" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="12" t="e">
+        <f>C34-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L34" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.1505735862108715</v>
+      </c>
+      <c r="M34" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-259.60754020868626</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="12">
+        <v>50.2</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12">
+        <v>22031</v>
+      </c>
+      <c r="G35" s="12">
+        <f t="shared" si="5"/>
+        <v>50.2</v>
+      </c>
+      <c r="H35" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.134103056106861</v>
+      </c>
+      <c r="I35" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>21759.549632569924</v>
+      </c>
+      <c r="J35" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="12" t="e">
+        <f>C35-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L35" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.134103056106861</v>
+      </c>
+      <c r="M35" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-271.45036743007586</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="12">
+        <v>51.4</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12">
+        <v>22581</v>
+      </c>
+      <c r="G36" s="12">
+        <f t="shared" si="5"/>
+        <v>51.4</v>
+      </c>
+      <c r="H36" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.232926236730929</v>
+      </c>
+      <c r="I36" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22286.606595898287</v>
+      </c>
+      <c r="J36" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="12" t="e">
+        <f>C36-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L36" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.232926236730929</v>
+      </c>
+      <c r="M36" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-294.3934041017128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="12">
+        <v>51.7</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12">
+        <v>22695</v>
+      </c>
+      <c r="G37" s="12">
+        <f t="shared" si="5"/>
+        <v>51.7</v>
+      </c>
+      <c r="H37" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.2576320318869465</v>
+      </c>
+      <c r="I37" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22418.370836730381</v>
+      </c>
+      <c r="J37" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="12" t="e">
+        <f>C37-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L37" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.2576320318869465</v>
+      </c>
+      <c r="M37" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-276.62916326961931</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="12">
+        <v>51.8</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12">
+        <v>22729</v>
+      </c>
+      <c r="G38" s="12">
+        <f t="shared" si="5"/>
+        <v>51.8</v>
+      </c>
+      <c r="H38" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.2658672969389517</v>
+      </c>
+      <c r="I38" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22462.292250341074</v>
+      </c>
+      <c r="J38" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="12" t="e">
+        <f>C38-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L38" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.2658672969389517</v>
+      </c>
+      <c r="M38" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-266.70774965892633</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="12">
+        <v>49.8</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12">
+        <v>21821</v>
+      </c>
+      <c r="G39" s="12">
+        <f t="shared" si="5"/>
+        <v>49.8</v>
+      </c>
+      <c r="H39" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.1011619958988375</v>
+      </c>
+      <c r="I39" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>21583.863978127134</v>
+      </c>
+      <c r="J39" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="12" t="e">
+        <f>C39-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L39" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.1011619958988375</v>
+      </c>
+      <c r="M39" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-237.13602187286597</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="12">
+        <v>49.6</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12">
+        <v>21779</v>
+      </c>
+      <c r="G40" s="12">
+        <f t="shared" si="5"/>
+        <v>49.6</v>
+      </c>
+      <c r="H40" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.0846914657948261</v>
+      </c>
+      <c r="I40" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>21496.021150905737</v>
+      </c>
+      <c r="J40" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="12" t="e">
+        <f>C40-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L40" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.0846914657948261</v>
+      </c>
+      <c r="M40" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-282.97884909426284</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="12">
+        <v>51.2</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12">
+        <v>22446</v>
+      </c>
+      <c r="G41" s="12">
+        <f t="shared" si="5"/>
+        <v>51.2</v>
+      </c>
+      <c r="H41" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.2164557066269177</v>
+      </c>
+      <c r="I41" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22198.763768676894</v>
+      </c>
+      <c r="J41" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="12" t="e">
+        <f>C41-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L41" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.2164557066269177</v>
+      </c>
+      <c r="M41" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-247.23623132310604</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="12">
+        <v>51.2</v>
+      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12">
+        <v>22500</v>
+      </c>
+      <c r="G42" s="12">
+        <f t="shared" si="5"/>
+        <v>51.2</v>
+      </c>
+      <c r="H42" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.2164557066269177</v>
+      </c>
+      <c r="I42" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22198.763768676894</v>
+      </c>
+      <c r="J42" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="12" t="e">
+        <f>C42-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L42" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.2164557066269177</v>
+      </c>
+      <c r="M42" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-301.23623132310604</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="12">
+        <v>51.3</v>
+      </c>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12">
+        <v>22519</v>
+      </c>
+      <c r="G43" s="12">
+        <f t="shared" si="5"/>
+        <v>51.3</v>
+      </c>
+      <c r="H43" s="12">
+        <f>Table43[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.2246909716789229</v>
+      </c>
+      <c r="I43" s="12">
+        <f>$Q$10+Table43[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>22242.685182287587</v>
+      </c>
+      <c r="J43" s="12">
+        <f>Table43[[#This Row],[Expected Divided Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="12" t="e">
+        <f>C43-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L43" s="12">
+        <f>Table43[[#This Row],[Adjusted Voltage]]-Table43[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.2246909716789229</v>
+      </c>
+      <c r="M43" s="12">
+        <f>Table43[[#This Row],[Adjusted Reading]]-Table43[[#This Row],[Actual ADC Reading]]</f>
+        <v>-276.31481771241306</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="P1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDD4075C-118D-4BC9-9E59-C74B697F8432}">
+  <dimension ref="A1:P50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="5" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2">
+        <v>25.2</v>
+      </c>
+      <c r="C2">
+        <f>B2/A2</f>
+        <v>22.909090909090907</v>
+      </c>
+      <c r="D2">
+        <v>6062</v>
+      </c>
+      <c r="E2">
+        <v>6067</v>
+      </c>
+      <c r="F2">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>8.2413054227789675E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>24.8</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C9" si="0">B3/A3</f>
+        <v>24.8</v>
+      </c>
+      <c r="D3">
+        <v>6846</v>
+      </c>
+      <c r="E3">
+        <v>6999</v>
+      </c>
+      <c r="F3">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>153</v>
+      </c>
+      <c r="G3">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>2.1860265752250321</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>25.1</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>25.1</v>
+      </c>
+      <c r="D4">
+        <v>7610</v>
+      </c>
+      <c r="E4">
+        <v>7777</v>
+      </c>
+      <c r="F4">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>167</v>
+      </c>
+      <c r="G4">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>2.1473575929021473</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1.3</v>
+      </c>
+      <c r="B5">
+        <v>25.3</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>19.46153846153846</v>
+      </c>
+      <c r="D5">
+        <v>6160</v>
+      </c>
+      <c r="E5">
+        <v>6305</v>
+      </c>
+      <c r="F5">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>145</v>
+      </c>
+      <c r="G5">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>2.2997620935765264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6">
+        <v>24.8</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>22.545454545454543</v>
+      </c>
+      <c r="D6">
+        <v>8584</v>
+      </c>
+      <c r="E6">
+        <v>8761</v>
+      </c>
+      <c r="F6">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>177</v>
+      </c>
+      <c r="G6">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>2.0203173153749572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0.8</v>
+      </c>
+      <c r="B7">
+        <v>24.5</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>30.625</v>
+      </c>
+      <c r="D7">
+        <v>10995</v>
+      </c>
+      <c r="E7">
+        <v>11197</v>
+      </c>
+      <c r="F7">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>202</v>
+      </c>
+      <c r="G7">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>1.804054657497544</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>0.8</v>
+      </c>
+      <c r="B8">
+        <v>24.3</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>30.375</v>
+      </c>
+      <c r="D8">
+        <v>11514</v>
+      </c>
+      <c r="E8">
+        <v>11735</v>
+      </c>
+      <c r="F8">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>221</v>
+      </c>
+      <c r="G8">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>1.8832552194290584</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0.8</v>
+      </c>
+      <c r="B9">
+        <v>24.5</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>30.625</v>
+      </c>
+      <c r="D9">
+        <v>11397</v>
+      </c>
+      <c r="E9">
+        <v>11609</v>
+      </c>
+      <c r="F9">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>212</v>
+      </c>
+      <c r="G9">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>1.8261693513653201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>25.1</v>
+      </c>
+      <c r="C10">
+        <f>B10/A10</f>
+        <v>25.1</v>
+      </c>
+      <c r="D10">
+        <v>7392</v>
+      </c>
+      <c r="E10">
+        <v>7548</v>
+      </c>
+      <c r="F10">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>156</v>
+      </c>
+      <c r="G10">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>2.066772655007949</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>25.3</v>
+      </c>
+      <c r="C11">
+        <f>B11/A11</f>
+        <v>25.3</v>
+      </c>
+      <c r="D11">
+        <v>6535</v>
+      </c>
+      <c r="E11">
+        <v>6696</v>
+      </c>
+      <c r="F11">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>161</v>
+      </c>
+      <c r="G11">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>2.40442054958184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B12">
+        <v>25.4</v>
+      </c>
+      <c r="C12">
+        <f>B12/A12</f>
+        <v>23.090909090909086</v>
+      </c>
+      <c r="D12">
+        <v>6039</v>
+      </c>
+      <c r="E12">
+        <v>6188</v>
+      </c>
+      <c r="F12">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>149</v>
+      </c>
+      <c r="G12">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>2.4078862314156431</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>-57</v>
+      </c>
+      <c r="E13">
+        <v>-22</v>
+      </c>
+      <c r="F13">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>35</v>
+      </c>
+      <c r="G13">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>-159.09090909090909</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <f>5/0.0001875</f>
+        <v>26666.666666666668</v>
+      </c>
+      <c r="E14">
+        <f>5/0.0001875</f>
+        <v>26666.666666666668</v>
+      </c>
+      <c r="F14">
+        <f>Table1[[#This Row],[Reading 2]]-Table1[[#This Row],[Reading 1]]</f>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f>100*Table1[[#This Row],[Reading Difference]]/Table1[[#This Row],[Reading 2]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="6">
+        <v>80</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" t="s">
+        <v>6</v>
+      </c>
+      <c r="M22" t="s">
+        <v>7</v>
+      </c>
+      <c r="O22" t="s">
+        <v>6</v>
+      </c>
+      <c r="P22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I23" s="9">
+        <v>363.17</v>
+      </c>
+      <c r="J23" s="9">
+        <v>-898.46</v>
+      </c>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9">
+        <f>IF(ISNUMBER(I23),$I23*M$21+$J23,"")</f>
+        <v>28155.140000000003</v>
+      </c>
+      <c r="M23" s="9">
+        <f>IF(ISNUMBER(I23),L23/(80000/3)*100,"")</f>
+        <v>105.58177500000001</v>
+      </c>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9">
+        <f>IF(ISNUMBER(I23),$I23*P$21+$J23, "")</f>
+        <v>17260.04</v>
+      </c>
+      <c r="P23" s="9">
+        <f>IF(ISNUMBER(I23),O23/(80000/3)*100, "")</f>
+        <v>64.725149999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <v>257.27999999999997</v>
+      </c>
+      <c r="J24">
+        <v>1087.0999999999999</v>
+      </c>
+      <c r="L24">
+        <f t="shared" ref="L24:L50" si="1">IF(ISNUMBER(I24),$I24*M$21+$J24,"")</f>
+        <v>21669.499999999996</v>
+      </c>
+      <c r="M24">
+        <f t="shared" ref="M24:M50" si="2">IF(ISNUMBER(I24),L24/(80000/3)*100,"")</f>
+        <v>81.26062499999999</v>
+      </c>
+      <c r="O24">
+        <f t="shared" ref="O24:O50" si="3">IF(ISNUMBER(I24),$I24*P$21+$J24, "")</f>
+        <v>13951.099999999999</v>
+      </c>
+      <c r="P24">
+        <f t="shared" ref="P24:P50" si="4">IF(ISNUMBER(I24),O24/(80000/3)*100, "")</f>
+        <v>52.316624999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="B25" s="2">
+        <v>25</v>
+      </c>
+      <c r="C25" s="2">
+        <f>B25/A25</f>
+        <v>41.666666666666671</v>
+      </c>
+      <c r="D25" s="2">
+        <v>8844</v>
+      </c>
+      <c r="E25" s="3">
+        <v>9005</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="9">
+        <v>363.88</v>
+      </c>
+      <c r="J25" s="9">
+        <v>-916.73</v>
+      </c>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9">
+        <f t="shared" si="1"/>
+        <v>28193.670000000002</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="2"/>
+        <v>105.72626250000002</v>
+      </c>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9">
+        <f t="shared" si="3"/>
+        <v>17277.27</v>
+      </c>
+      <c r="P25" s="9">
+        <f t="shared" si="4"/>
+        <v>64.789762500000009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="B26" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="C26" s="2">
+        <f>B26/A26</f>
+        <v>31.875</v>
+      </c>
+      <c r="D26" s="2">
+        <v>6136</v>
+      </c>
+      <c r="E26" s="3">
+        <v>6276</v>
+      </c>
+      <c r="H26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26">
+        <v>328.52</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>26281.599999999999</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="2"/>
+        <v>98.555999999999983</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="3"/>
+        <v>16426</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="4"/>
+        <v>61.597499999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H27" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" s="9">
+        <v>363.17</v>
+      </c>
+      <c r="J27" s="9">
+        <v>-898.46</v>
+      </c>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9">
+        <f t="shared" si="1"/>
+        <v>28155.140000000003</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="2"/>
+        <v>105.58177500000001</v>
+      </c>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9">
+        <f t="shared" si="3"/>
+        <v>17260.04</v>
+      </c>
+      <c r="P27" s="9">
+        <f t="shared" si="4"/>
+        <v>64.725149999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H28" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28">
+        <v>262.64</v>
+      </c>
+      <c r="J28">
+        <v>1364.8</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>22375.999999999996</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="2"/>
+        <v>83.909999999999982</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="3"/>
+        <v>14496.8</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="4"/>
+        <v>54.362999999999992</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I31" t="s">
+        <v>8</v>
+      </c>
+      <c r="J31" t="s">
+        <v>9</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H32" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="9">
+        <v>385.19</v>
+      </c>
+      <c r="J32" s="9">
+        <v>-932.7</v>
+      </c>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9">
+        <f t="shared" si="1"/>
+        <v>29882.5</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" si="2"/>
+        <v>112.059375</v>
+      </c>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9">
+        <f t="shared" si="3"/>
+        <v>18326.8</v>
+      </c>
+      <c r="P32" s="9">
+        <f t="shared" si="4"/>
+        <v>68.725499999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="H33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33">
+        <v>322.22000000000003</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>25777.600000000002</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="2"/>
+        <v>96.666000000000011</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="3"/>
+        <v>16111.000000000002</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="4"/>
+        <v>60.416250000000005</v>
+      </c>
+    </row>
+    <row r="34" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="H34" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" s="9">
+        <v>356.37</v>
+      </c>
+      <c r="J34" s="9">
+        <v>-885.38</v>
+      </c>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9">
+        <f t="shared" si="1"/>
+        <v>27624.219999999998</v>
+      </c>
+      <c r="M34" s="9">
+        <f t="shared" si="2"/>
+        <v>103.59082499999998</v>
+      </c>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9">
+        <f t="shared" si="3"/>
+        <v>16933.12</v>
+      </c>
+      <c r="P34" s="9">
+        <f t="shared" si="4"/>
+        <v>63.499199999999988</v>
+      </c>
+    </row>
+    <row r="35" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="H35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I35">
+        <v>263.67</v>
+      </c>
+      <c r="J35">
+        <v>1197.4000000000001</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="1"/>
+        <v>22291.000000000004</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="2"/>
+        <v>83.591250000000002</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="3"/>
+        <v>14380.9</v>
+      </c>
+      <c r="P35">
+        <f t="shared" si="4"/>
+        <v>53.928374999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L38" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L39" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L40" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L41" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L42" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L43" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L44" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L45" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L46" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L47" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="L48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="12:16" x14ac:dyDescent="0.3">
+      <c r="L49" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="12:16" x14ac:dyDescent="0.3">
+      <c r="L50" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC7156C4-D780-4AF4-81FE-0216F154F497}">
+  <dimension ref="A1:U16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="22.109375" customWidth="1"/>
+    <col min="8" max="8" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.77734375" customWidth="1"/>
+    <col min="10" max="10" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" customWidth="1"/>
+    <col min="12" max="12" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="21.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="11"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>57</v>
+      </c>
+      <c r="B2">
+        <f t="shared" ref="B2:B16" si="0">A2*$Q$5</f>
+        <v>4.75</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:C16" si="1">B2/$Q$2</f>
+        <v>25333.333333333332</v>
+      </c>
+      <c r="D2">
+        <v>56.325000000000003</v>
+      </c>
+      <c r="E2">
+        <f t="shared" ref="E2:E16" si="2">D2*$Q$5</f>
+        <v>4.6937499999999996</v>
+      </c>
+      <c r="F2">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>25033.333333333332</v>
+      </c>
+      <c r="G2">
+        <f t="shared" ref="G2:G16" si="3">A2-D2</f>
+        <v>0.67499999999999716</v>
+      </c>
+      <c r="H2">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.6941010796432483</v>
+      </c>
+      <c r="I2">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>24746.205758097323</v>
+      </c>
+      <c r="J2">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.6250000000000355E-2</v>
+      </c>
+      <c r="K2">
+        <f t="shared" ref="K2:K16" si="4">C2-F2</f>
+        <v>300</v>
+      </c>
+      <c r="L2">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>3.5107964324865293E-4</v>
+      </c>
+      <c r="M2">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-287.12757523600885</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>1.875E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>56.3</v>
+      </c>
+      <c r="B3">
+        <f t="shared" si="0"/>
+        <v>4.6916666666666664</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="1"/>
+        <v>25022.222222222219</v>
+      </c>
+      <c r="D3">
+        <v>55.610999999999997</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="2"/>
+        <v>4.6342499999999998</v>
+      </c>
+      <c r="F3">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24716</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="3"/>
+        <v>0.68900000000000006</v>
+      </c>
+      <c r="H3">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.6364542242792082</v>
+      </c>
+      <c r="I3">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>24438.755862822443</v>
+      </c>
+      <c r="J3">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.7416666666666671E-2</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="4"/>
+        <v>306.22222222221899</v>
+      </c>
+      <c r="L3">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>2.204224279208411E-3</v>
+      </c>
+      <c r="M3">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-277.24413717755669</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>56.3</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>4.6916666666666664</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>25022.222222222219</v>
+      </c>
+      <c r="D4">
+        <v>55.624499999999998</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="2"/>
+        <v>4.6353749999999998</v>
+      </c>
+      <c r="F4">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24722</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="3"/>
+        <v>0.67549999999999955</v>
+      </c>
+      <c r="H4">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.6364542242792082</v>
+      </c>
+      <c r="I4">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>24438.755862822443</v>
+      </c>
+      <c r="J4">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.6291666666666629E-2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="4"/>
+        <v>300.22222222221899</v>
+      </c>
+      <c r="L4">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>1.0792242792083684E-3</v>
+      </c>
+      <c r="M4">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-283.24413717755669</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>56.2</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>4.6833333333333336</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>24977.777777777777</v>
+      </c>
+      <c r="D5">
+        <v>55.557000000000002</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>4.6297499999999996</v>
+      </c>
+      <c r="F5">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24691.999999999996</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="3"/>
+        <v>0.64300000000000068</v>
+      </c>
+      <c r="H5">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.6282189592272029</v>
+      </c>
+      <c r="I5">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>24394.83444921175</v>
+      </c>
+      <c r="J5">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.3583333333333982E-2</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="4"/>
+        <v>285.77777777778101</v>
+      </c>
+      <c r="L5">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>-1.5310407727966435E-3</v>
+      </c>
+      <c r="M5">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-297.16555078824604</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="6">
+        <f>Q4/(Q4+Q3)</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>56.2</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>4.6833333333333336</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>24977.777777777777</v>
+      </c>
+      <c r="D6">
+        <v>55.58625</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>4.6321874999999997</v>
+      </c>
+      <c r="F6">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24704.999999999996</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="3"/>
+        <v>0.61375000000000313</v>
+      </c>
+      <c r="H6">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.6282189592272029</v>
+      </c>
+      <c r="I6">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>24394.83444921175</v>
+      </c>
+      <c r="J6">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.114583333333389E-2</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="4"/>
+        <v>272.77777777778101</v>
+      </c>
+      <c r="L6">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>-3.9685407727967359E-3</v>
+      </c>
+      <c r="M6">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-310.16555078824604</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>55.8</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>4.6499999999999995</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>24799.999999999996</v>
+      </c>
+      <c r="D7">
+        <v>55.094999999999999</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="2"/>
+        <v>4.5912499999999996</v>
+      </c>
+      <c r="F7">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24486.666666666664</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="3"/>
+        <v>0.70499999999999829</v>
+      </c>
+      <c r="H7">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.5952778990191794</v>
+      </c>
+      <c r="I7">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>24219.148794768957</v>
+      </c>
+      <c r="J7">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.8749999999999858E-2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="4"/>
+        <v>313.33333333333212</v>
+      </c>
+      <c r="L7">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.0278990191797703E-3</v>
+      </c>
+      <c r="M7">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-267.51787189770766</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>111429</v>
+      </c>
+      <c r="R7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>55.4</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>4.6166666666666663</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>24622.222222222219</v>
+      </c>
+      <c r="D8">
+        <v>54.84</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>4.57</v>
+      </c>
+      <c r="F8">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24373.333333333336</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="3"/>
+        <v>0.55999999999999517</v>
+      </c>
+      <c r="H8">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.5623368388111567</v>
+      </c>
+      <c r="I8">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>24043.46314032617</v>
+      </c>
+      <c r="J8">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.6666666666665968E-2</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="4"/>
+        <v>248.88888888888323</v>
+      </c>
+      <c r="L8">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>-7.6631611888435813E-3</v>
+      </c>
+      <c r="M8">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-329.87019300716565</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>55.3</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>4.6083333333333325</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>24577.777777777774</v>
+      </c>
+      <c r="D9">
+        <v>54.641249999999999</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>4.5534374999999994</v>
+      </c>
+      <c r="F9">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24284.999999999996</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="3"/>
+        <v>0.65874999999999773</v>
+      </c>
+      <c r="H9">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.5541015737591506</v>
+      </c>
+      <c r="I9">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23999.54172671547</v>
+      </c>
+      <c r="J9">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.4895833333333144E-2</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="4"/>
+        <v>292.77777777777737</v>
+      </c>
+      <c r="L9">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>6.6407375915122913E-4</v>
+      </c>
+      <c r="M9">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-285.45827328452651</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9">
+        <f>Q8/(Q8+Q7)</f>
+        <v>8.2352650520056983E-2</v>
+      </c>
+      <c r="R9" s="6">
+        <v>8.2352999999999996E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>55.3</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>4.6083333333333325</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>24577.777777777774</v>
+      </c>
+      <c r="D10">
+        <v>54.683999999999997</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>4.5569999999999995</v>
+      </c>
+      <c r="F10">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24303.999999999996</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="3"/>
+        <v>0.61599999999999966</v>
+      </c>
+      <c r="H10">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.5541015737591506</v>
+      </c>
+      <c r="I10">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23999.54172671547</v>
+      </c>
+      <c r="J10">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.1333333333333009E-2</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="4"/>
+        <v>273.77777777777737</v>
+      </c>
+      <c r="L10">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>-2.8984262408489059E-3</v>
+      </c>
+      <c r="M10">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-304.45827328452651</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>-289</v>
+      </c>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>55.3</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>4.6083333333333325</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>24577.777777777774</v>
+      </c>
+      <c r="D11">
+        <v>54.704250000000002</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>4.5586874999999996</v>
+      </c>
+      <c r="F11">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24312.999999999996</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="3"/>
+        <v>0.59574999999999534</v>
+      </c>
+      <c r="H11">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.5541015737591506</v>
+      </c>
+      <c r="I11">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23999.54172671547</v>
+      </c>
+      <c r="J11">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.9645833333332945E-2</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="4"/>
+        <v>264.77777777777737</v>
+      </c>
+      <c r="L11">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>-4.5859262408489698E-3</v>
+      </c>
+      <c r="M11">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-313.45827328452651</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>54.8</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>4.5666666666666664</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>24355.555555555555</v>
+      </c>
+      <c r="D12">
+        <v>54.065249999999999</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>4.5054374999999993</v>
+      </c>
+      <c r="F12">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24028.999999999996</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="3"/>
+        <v>0.73474999999999824</v>
+      </c>
+      <c r="H12">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.5129252484991227</v>
+      </c>
+      <c r="I12">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23779.934658661987</v>
+      </c>
+      <c r="J12">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>6.1229166666667112E-2</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="4"/>
+        <v>326.55555555555839</v>
+      </c>
+      <c r="L12">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>7.48774849912337E-3</v>
+      </c>
+      <c r="M12">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-249.0653413380096</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>54.6</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>4.55</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="1"/>
+        <v>24266.666666666664</v>
+      </c>
+      <c r="D13">
+        <v>53.939250000000001</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>4.4949374999999998</v>
+      </c>
+      <c r="F13">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>23973</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="3"/>
+        <v>0.66075000000000017</v>
+      </c>
+      <c r="H13">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.4964547183951113</v>
+      </c>
+      <c r="I13">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23692.091831440594</v>
+      </c>
+      <c r="J13">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.5062500000000014E-2</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="4"/>
+        <v>293.66666666666424</v>
+      </c>
+      <c r="L13">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>1.5172183951115414E-3</v>
+      </c>
+      <c r="M13">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-280.90816855940648</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" s="6">
+        <f>AVERAGE(Table4[Adjusted Voltage Difference])</f>
+        <v>-1.2416206178045287E-5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>54.6</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>4.55</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>24266.666666666664</v>
+      </c>
+      <c r="D14">
+        <v>54.020249999999997</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>4.5016874999999992</v>
+      </c>
+      <c r="F14">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>24008.999999999996</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="3"/>
+        <v>0.57975000000000421</v>
+      </c>
+      <c r="H14">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.4964547183951113</v>
+      </c>
+      <c r="I14">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23692.091831440594</v>
+      </c>
+      <c r="J14">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>4.8312500000000647E-2</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="4"/>
+        <v>257.66666666666788</v>
+      </c>
+      <c r="L14">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>-5.2327816048878262E-3</v>
+      </c>
+      <c r="M14">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-316.90816855940284</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14" s="6">
+        <f>AVERAGE(Table4[Adjusted Reading Difference])</f>
+        <v>-289.06621976628304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>53.8</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>4.4833333333333325</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="1"/>
+        <v>23911.111111111106</v>
+      </c>
+      <c r="D15">
+        <v>53.091000000000001</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>4.4242499999999998</v>
+      </c>
+      <c r="F15">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>23596</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="3"/>
+        <v>0.70899999999999608</v>
+      </c>
+      <c r="H15">
+        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
+        <v>4.4305725979790651</v>
+      </c>
+      <c r="I15">
+        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
+        <v>23340.720522555013</v>
+      </c>
+      <c r="J15">
+        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>5.908333333333271E-2</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="4"/>
+        <v>315.11111111110586</v>
+      </c>
+      <c r="L15">
+        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
+        <v>6.3225979790653142E-3</v>
+      </c>
+      <c r="M15">
+        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
+        <v>-255.2794774449867</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>53.6</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>4.4666666666666668</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>23822.222222222223</v>
+      </c>
+      <c r="D16">
+        <v>52.944749999999999</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>4.4120624999999993</v>
+      </c>
+      <c r="F16">
+        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
+        <v>23530.999999999996</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="3"/>
+        <v>0.65525000000000233</v>
+      </c>
+      <c r="H16">
         <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
         <v>4.4141020678750547</v>
       </c>
@@ -7003,77 +12092,6 @@
       <c r="M16">
         <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
         <v>-278.12230466637266</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>58.4</v>
-      </c>
-      <c r="B26" s="2">
-        <f>A26*$Q$5</f>
-        <v>4.8666666666666663</v>
-      </c>
-      <c r="C26" s="2">
-        <f t="shared" ref="C26" si="5">B26/$Q$2</f>
-        <v>25955.555555555551</v>
-      </c>
-      <c r="D26" s="2">
-        <v>57.46725</v>
-      </c>
-      <c r="E26" s="2">
-        <f>D26*$Q$5</f>
-        <v>4.7889374999999994</v>
-      </c>
-      <c r="F26" s="2" t="e">
-        <f>Table4[[#This Row],[Actual Divided Voltage]]/$Q$2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G26" s="2">
-        <f>A26-D26</f>
-        <v>0.93274999999999864</v>
-      </c>
-      <c r="H26" s="2" t="e">
-        <f>Table4[[#This Row],[Multimeter]]*$Q$9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I26" s="2" t="e">
-        <f>$Q$10+Table4[[#This Row],[Adjusted Voltage]]/$Q$2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J26" s="2" t="e">
-        <f>Table4[[#This Row],[Expected Divided Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K26" s="2" t="e">
-        <f>C26-F26</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L26" s="2" t="e">
-        <f>Table4[[#This Row],[Adjusted Voltage]]-Table4[[#This Row],[Actual Divided Voltage]]</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M26" s="3" t="e">
-        <f>Table4[[#This Row],[Adjusted Reading]]-Table4[[#This Row],[Actual ADC Reading]]</f>
-        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
